--- a/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
+++ b/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,15 +431,10 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Observados</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>Chao1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
@@ -455,12 +450,9 @@
         <v>4.727913615323832</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9818233613955352</v>
-      </c>
-      <c r="D2" t="n">
         <v>233</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -476,12 +468,9 @@
         <v>4.37342753930256</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9595839837589004</v>
-      </c>
-      <c r="D3" t="n">
         <v>203</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -497,14 +486,11 @@
         <v>4.268113636013911</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9621993449367908</v>
-      </c>
-      <c r="D4" t="n">
         <v>158</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -518,14 +504,11 @@
         <v>4.019301000420485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9585912556041788</v>
-      </c>
-      <c r="D5" t="n">
         <v>112</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -539,14 +522,11 @@
         <v>4.680088140459228</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9723289162052944</v>
-      </c>
-      <c r="D6" t="n">
         <v>260</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -560,12 +540,9 @@
         <v>4.643242956666275</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9743035026411844</v>
-      </c>
-      <c r="D7" t="n">
         <v>219</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -581,12 +558,9 @@
         <v>4.515375378087538</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9690128980909134</v>
-      </c>
-      <c r="D8" t="n">
         <v>217</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -602,14 +576,11 @@
         <v>4.601787336159488</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9682982797847656</v>
-      </c>
-      <c r="D9" t="n">
         <v>252</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -623,14 +594,11 @@
         <v>4.675305389147026</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9705240292591616</v>
-      </c>
-      <c r="D10" t="n">
         <v>266</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -644,12 +612,9 @@
         <v>4.436698877796648</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9646834284169216</v>
-      </c>
-      <c r="D11" t="n">
         <v>224</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -665,12 +630,9 @@
         <v>4.987932758016299</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9864593000436572</v>
-      </c>
-      <c r="D12" t="n">
         <v>270</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -686,14 +648,11 @@
         <v>4.401628644301807</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9661495561074924</v>
-      </c>
-      <c r="D13" t="n">
         <v>180</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -707,14 +666,11 @@
         <v>4.747930759871308</v>
       </c>
       <c r="C14" t="n">
-        <v>0.984348063851576</v>
-      </c>
-      <c r="D14" t="n">
         <v>189</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -728,14 +684,11 @@
         <v>4.785548839520375</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9815275535976083</v>
-      </c>
-      <c r="D15" t="n">
         <v>220</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -749,12 +702,9 @@
         <v>4.969144551216438</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9880342781366822</v>
-      </c>
-      <c r="D16" t="n">
         <v>234</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -770,12 +720,9 @@
         <v>4.964239510317395</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9876436016364278</v>
-      </c>
-      <c r="D17" t="n">
         <v>240</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -791,14 +738,11 @@
         <v>5.139509278002505</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9905810493401536</v>
-      </c>
-      <c r="D18" t="n">
         <v>277</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -812,14 +756,11 @@
         <v>5.025267768569615</v>
       </c>
       <c r="C19" t="n">
-        <v>0.988903600356925</v>
-      </c>
-      <c r="D19" t="n">
         <v>258</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -833,12 +774,9 @@
         <v>4.840966567376717</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9842628132387724</v>
-      </c>
-      <c r="D20" t="n">
         <v>239</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -854,12 +792,9 @@
         <v>4.700801148148279</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9693781710888032</v>
-      </c>
-      <c r="D21" t="n">
         <v>283</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -875,14 +810,11 @@
         <v>4.057676006429582</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9545139318813272</v>
-      </c>
-      <c r="D22" t="n">
         <v>131</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -896,14 +828,11 @@
         <v>4.400390430211783</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9678631799175732</v>
-      </c>
-      <c r="D23" t="n">
         <v>179</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -917,12 +846,9 @@
         <v>4.415815763338032</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9650582261752388</v>
-      </c>
-      <c r="D24" t="n">
         <v>201</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -938,14 +864,11 @@
         <v>4.853747606986211</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9780574505045432</v>
-      </c>
-      <c r="D25" t="n">
         <v>289</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -959,14 +882,11 @@
         <v>4.355451529426168</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9658314914311978</v>
-      </c>
-      <c r="D26" t="n">
         <v>179</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -980,12 +900,9 @@
         <v>4.163731175537002</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9613969871002348</v>
-      </c>
-      <c r="D27" t="n">
         <v>134</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1001,14 +918,11 @@
         <v>4.811730729087116</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9845922673592008</v>
-      </c>
-      <c r="D28" t="n">
         <v>223</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1022,14 +936,11 @@
         <v>4.430842808299833</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9663694285795896</v>
-      </c>
-      <c r="D29" t="n">
         <v>198</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1043,12 +954,9 @@
         <v>4.87415521476794</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9846016181050332</v>
-      </c>
-      <c r="D30" t="n">
         <v>248</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1064,12 +972,9 @@
         <v>4.881550062673192</v>
       </c>
       <c r="C31" t="n">
-        <v>0.985401710192078</v>
-      </c>
-      <c r="D31" t="n">
         <v>242</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1085,12 +990,9 @@
         <v>4.284590212347853</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9712230364493182</v>
-      </c>
-      <c r="D32" t="n">
         <v>153</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1106,12 +1008,9 @@
         <v>4.540152916504041</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9708091126355658</v>
-      </c>
-      <c r="D33" t="n">
         <v>246</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1127,14 +1026,11 @@
         <v>3.799112558475625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.94621143489754</v>
-      </c>
-      <c r="D34" t="n">
         <v>98</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1044,9 @@
         <v>4.329158971727574</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9663743991563868</v>
-      </c>
-      <c r="D35" t="n">
         <v>158</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1169,12 +1062,9 @@
         <v>4.42576867445196</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9652718932704882</v>
-      </c>
-      <c r="D36" t="n">
         <v>201</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1190,12 +1080,9 @@
         <v>4.61782104673466</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9696772147084194</v>
-      </c>
-      <c r="D37" t="n">
         <v>257</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1211,14 +1098,11 @@
         <v>4.254498613836764</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9648291308071676</v>
-      </c>
-      <c r="D38" t="n">
         <v>152</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1116,9 @@
         <v>4.499986607347755</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9675662547703084</v>
-      </c>
-      <c r="D39" t="n">
         <v>216</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1253,14 +1134,11 @@
         <v>3.954052229406671</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9526314537005802</v>
-      </c>
-      <c r="D40" t="n">
         <v>112</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1274,14 +1152,11 @@
         <v>4.792466432912013</v>
       </c>
       <c r="C41" t="n">
-        <v>0.97874392094326</v>
-      </c>
-      <c r="D41" t="n">
         <v>279</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1170,9 @@
         <v>4.291921695864335</v>
       </c>
       <c r="C42" t="n">
-        <v>0.968457696359822</v>
-      </c>
-      <c r="D42" t="n">
         <v>143</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1316,14 +1188,11 @@
         <v>4.887899818905326</v>
       </c>
       <c r="C43" t="n">
-        <v>0.977240807168744</v>
-      </c>
-      <c r="D43" t="n">
         <v>319</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1337,14 +1206,11 @@
         <v>4.491517207814678</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9689940517355712</v>
-      </c>
-      <c r="D44" t="n">
         <v>196</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1358,14 +1224,11 @@
         <v>4.213295785027315</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9730485804853222</v>
-      </c>
-      <c r="D45" t="n">
         <v>122</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1242,9 @@
         <v>4.430286506957092</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9714940992998384</v>
-      </c>
-      <c r="D46" t="n">
         <v>235</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1400,12 +1260,9 @@
         <v>4.639149529513643</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9699051698065956</v>
-      </c>
-      <c r="D47" t="n">
         <v>269</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1421,14 +1278,11 @@
         <v>4.536588828758447</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9671712105552724</v>
-      </c>
-      <c r="D48" t="n">
         <v>225</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1442,14 +1296,11 @@
         <v>4.32887023563142</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9622626114595932</v>
-      </c>
-      <c r="D49" t="n">
         <v>186</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1314,9 @@
         <v>4.373133333980642</v>
       </c>
       <c r="C50" t="n">
-        <v>0.960295603886676</v>
-      </c>
-      <c r="D50" t="n">
         <v>217</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1484,12 +1332,9 @@
         <v>5.008456459697701</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9872026593528956</v>
-      </c>
-      <c r="D51" t="n">
         <v>273</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1505,14 +1350,11 @@
         <v>4.851250460746227</v>
       </c>
       <c r="C52" t="n">
-        <v>0.987522573569022</v>
-      </c>
-      <c r="D52" t="n">
         <v>191</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1526,14 +1368,11 @@
         <v>4.448409326496159</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9804160758686452</v>
-      </c>
-      <c r="D53" t="n">
         <v>134</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1547,14 +1386,11 @@
         <v>4.590282721588087</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9722686823557062</v>
-      </c>
-      <c r="D54" t="n">
         <v>217</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1404,9 @@
         <v>4.808761220034736</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9837778070504468</v>
-      </c>
-      <c r="D55" t="n">
         <v>203</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1589,12 +1422,9 @@
         <v>4.519958174258856</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9761185393593248</v>
-      </c>
-      <c r="D56" t="n">
         <v>185</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1610,14 +1440,11 @@
         <v>4.7948339494373</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9864890724676432</v>
-      </c>
-      <c r="D57" t="n">
         <v>185</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1631,14 +1458,11 @@
         <v>4.936613990224418</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9892082232339195</v>
-      </c>
-      <c r="D58" t="n">
         <v>203</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1476,9 @@
         <v>4.964219265592137</v>
       </c>
       <c r="C59" t="n">
-        <v>0.988269478480832</v>
-      </c>
-      <c r="D59" t="n">
         <v>231</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1673,12 +1494,9 @@
         <v>4.27416907269034</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9608808168591484</v>
-      </c>
-      <c r="D60" t="n">
         <v>166</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1694,14 +1512,11 @@
         <v>4.213304207885006</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9600681362131128</v>
-      </c>
-      <c r="D61" t="n">
         <v>153</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1715,14 +1530,11 @@
         <v>4.354497495741709</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9643847826480852</v>
-      </c>
-      <c r="D62" t="n">
         <v>168</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1548,9 @@
         <v>4.631200953805885</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9730415519237086</v>
-      </c>
-      <c r="D63" t="n">
         <v>219</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1757,12 +1566,9 @@
         <v>4.241500386030912</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9665287776847586</v>
-      </c>
-      <c r="D64" t="n">
         <v>137</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1778,12 +1584,9 @@
         <v>4.122958924626568</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9663188839167064</v>
-      </c>
-      <c r="D65" t="n">
         <v>113</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -1799,14 +1602,11 @@
         <v>4.428978985527641</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9664863259579231</v>
-      </c>
-      <c r="D66" t="n">
         <v>193</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1820,14 +1620,11 @@
         <v>4.45235964743468</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9671459419568974</v>
-      </c>
-      <c r="D67" t="n">
         <v>192</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>CS</t>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -1841,14 +1638,11 @@
         <v>4.018109432643039</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9586700472047608</v>
-      </c>
-      <c r="D68" t="n">
         <v>108</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1862,14 +1656,11 @@
         <v>4.850724154771048</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9849157457414252</v>
-      </c>
-      <c r="D69" t="n">
         <v>223</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1674,9 @@
         <v>5.18004509987883</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9900539626060938</v>
-      </c>
-      <c r="D70" t="n">
         <v>295</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1904,12 +1692,9 @@
         <v>5.177522108733596</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9893964430535704</v>
-      </c>
-      <c r="D71" t="n">
         <v>308</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1925,14 +1710,11 @@
         <v>4.819807792710856</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9872906755382244</v>
-      </c>
-      <c r="D72" t="n">
         <v>183</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1946,14 +1728,11 @@
         <v>5.033483219688343</v>
       </c>
       <c r="C73" t="n">
-        <v>0.987677538470097</v>
-      </c>
-      <c r="D73" t="n">
         <v>260</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1746,9 @@
         <v>4.997528953831365</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9900450164124014</v>
-      </c>
-      <c r="D74" t="n">
         <v>212</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -1988,12 +1764,9 @@
         <v>4.755990553387885</v>
       </c>
       <c r="C75" t="n">
-        <v>0.986165974832938</v>
-      </c>
-      <c r="D75" t="n">
         <v>174</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2009,14 +1782,11 @@
         <v>3.835042688837456</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9572542943723286</v>
-      </c>
-      <c r="D76" t="n">
         <v>83</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2030,14 +1800,11 @@
         <v>5.122212643389764</v>
       </c>
       <c r="C77" t="n">
-        <v>0.98836216949314</v>
-      </c>
-      <c r="D77" t="n">
         <v>320</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2051,14 +1818,11 @@
         <v>4.451409707690437</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9615006453220528</v>
-      </c>
-      <c r="D78" t="n">
         <v>230</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2072,12 +1836,9 @@
         <v>4.913172138488332</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9839721768068892</v>
-      </c>
-      <c r="D79" t="n">
         <v>272</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2093,12 +1854,9 @@
         <v>4.707035337689703</v>
       </c>
       <c r="C80" t="n">
-        <v>0.979318553428944</v>
-      </c>
-      <c r="D80" t="n">
         <v>222</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2114,14 +1872,11 @@
         <v>4.600365112815678</v>
       </c>
       <c r="C81" t="n">
-        <v>0.982083390579621</v>
-      </c>
-      <c r="D81" t="n">
         <v>172</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2135,12 +1890,9 @@
         <v>4.483702741359124</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9691782154917524</v>
-      </c>
-      <c r="D82" t="n">
         <v>184</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2156,12 +1908,9 @@
         <v>4.221860899651439</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9604024402483048</v>
-      </c>
-      <c r="D83" t="n">
         <v>154</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2177,14 +1926,11 @@
         <v>4.203876500464943</v>
       </c>
       <c r="C84" t="n">
-        <v>0.978657603297686</v>
-      </c>
-      <c r="D84" t="n">
         <v>102</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -2198,14 +1944,11 @@
         <v>4.075283745806841</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9535762281327984</v>
-      </c>
-      <c r="D85" t="n">
         <v>141</v>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2219,12 +1962,9 @@
         <v>4.460856250790559</v>
       </c>
       <c r="C86" t="n">
-        <v>0.977926518500195</v>
-      </c>
-      <c r="D86" t="n">
         <v>173</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>CSSwP</t>
         </is>
@@ -2240,14 +1980,11 @@
         <v>4.462086775311617</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9761037662412548</v>
-      </c>
-      <c r="D87" t="n">
         <v>189</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sin metadata</t>
         </is>
       </c>
     </row>
@@ -2261,14 +1998,11 @@
         <v>4.004017774919607</v>
       </c>
       <c r="C88" t="n">
-        <v>0.9570559004673568</v>
-      </c>
-      <c r="D88" t="n">
         <v>151</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2282,14 +2016,11 @@
         <v>4.566283715768781</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9637022520347004</v>
-      </c>
-      <c r="D89" t="n">
         <v>270</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>CSSwP</t>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,36 +2062,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1060</v>
+        <v>903</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4451076222831162</v>
+        <v>0.8560717948523305</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Observados</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7416719182569518</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chao1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1072</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.387688654980924</v>
+        <v>0.5115215916067976</v>
       </c>
     </row>
   </sheetData>
@@ -2442,14 +2160,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3556316220333445</v>
+        <v>-0.3556316220333446</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0116826198988604</v>
+        <v>0.01168261989886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2463,11 +2181,11 @@
         <v>-0.3666950874251473</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0360504689195918</v>
+        <v>0.0360504689195915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2481,11 +2199,11 @@
         <v>-0.3389182162553093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0012785690026344</v>
+        <v>0.0012785690026345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2257,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2275,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2329,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2625,11 +2343,11 @@
         <v>0.4777117795488325</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.048642469917585</v>
+        <v>-0.0486424699175851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2640,14 +2358,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4427576725726543</v>
+        <v>0.4427576725726542</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0222657017554232</v>
+        <v>-0.0222657017554233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2697,11 +2415,11 @@
         <v>0.4415395319018175</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1097574462742457</v>
+        <v>-0.1097574462742458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2437,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2451,7 @@
         <v>0.4671789981864702</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0660703758122593</v>
+        <v>-0.0660703758122592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,7 +2491,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2509,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2545,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2563,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2877,11 +2595,11 @@
         <v>0.510907172899751</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0269048572763981</v>
+        <v>0.0269048572763982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2617,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2649,7 @@
         <v>0.5279040109553492</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09245572520330041</v>
+        <v>0.0924557252033005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2989,7 +2707,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3061,7 +2779,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3097,7 +2815,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3108,14 +2826,14 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5214751954409831</v>
+        <v>0.5214751954409832</v>
       </c>
       <c r="C41" t="n">
         <v>0.0726001173259738</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3129,7 +2847,7 @@
         <v>-0.3690733252201084</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0264440150339183</v>
+        <v>0.0264440150339182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3151,7 +2869,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3169,7 +2887,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3187,7 +2905,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3198,10 +2916,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5209584369697391</v>
+        <v>0.5209584369697392</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3341340705637853</v>
+        <v>0.3341340705637855</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3219,7 +2937,7 @@
         <v>-0.34808972601082</v>
       </c>
       <c r="C47" t="n">
-        <v>0.007876875096746901</v>
+        <v>0.007876875096746999</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3241,7 +2959,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3255,11 +2973,11 @@
         <v>-0.3685368792531704</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0167160696419433</v>
+        <v>0.0167160696419432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3309,11 +3027,11 @@
         <v>0.3616990651919713</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1644188583084117</v>
+        <v>-0.1644188583084118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3327,11 +3045,11 @@
         <v>0.3826020945880666</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2002113428306418</v>
+        <v>-0.200211342830642</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3067,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3096,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3497443264740414</v>
+        <v>0.3497443264740413</v>
       </c>
       <c r="C56" t="n">
         <v>-0.2045475082327115</v>
@@ -3403,7 +3121,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3417,11 +3135,11 @@
         <v>0.3564142082979051</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1849198127174697</v>
+        <v>-0.1849198127174698</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3153,7 @@
         <v>0.2291071241196891</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1852767249133001</v>
+        <v>-0.1852767249133</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3475,7 +3193,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3486,14 +3204,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3585738156047759</v>
+        <v>-0.358573815604776</v>
       </c>
       <c r="C62" t="n">
         <v>0.0066603283857315</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3225,7 @@
         <v>-0.3416526068191004</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.011030622373359</v>
+        <v>-0.0110306223733589</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3565,7 +3283,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3301,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -3597,11 +3315,11 @@
         <v>-0.3736054671312626</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0279351430473872</v>
+        <v>0.0279351430473871</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3337,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3348,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.35872381829562</v>
+        <v>0.3587238182956199</v>
       </c>
       <c r="C70" t="n">
         <v>-0.1822393227536042</v>
@@ -3651,7 +3369,7 @@
         <v>0.3601314390630981</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1577002433638206</v>
+        <v>-0.1577002433638207</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3673,7 +3391,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3409,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3463,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3759,11 +3477,11 @@
         <v>0.375820968815208</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1799824499823777</v>
+        <v>-0.1799824499823776</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3499,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3513,7 @@
         <v>0.5137857081071431</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1026077482150583</v>
+        <v>0.1026077482150584</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3831,11 +3549,11 @@
         <v>0.5255764809134581</v>
       </c>
       <c r="C81" t="n">
-        <v>0.009390525371448299</v>
+        <v>0.0093905253714484</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3885,11 +3603,11 @@
         <v>0.0687644083511052</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2726312085318035</v>
+        <v>0.2726312085318033</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3625,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3639,7 @@
         <v>0.4996068617951564</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3478417181300082</v>
+        <v>0.3478417181300083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3939,11 +3657,11 @@
         <v>0.5135454384737363</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3606380791457187</v>
+        <v>0.3606380791457189</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>Sin metadata</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3679,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3697,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>

--- a/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
+++ b/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sin metadata</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>903</v>
+        <v>928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8560717948523305</v>
+        <v>0.8818941220889477</v>
       </c>
     </row>
     <row r="3">
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1001</v>
+        <v>1029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5115215916067976</v>
+        <v>0.4836411750614761</v>
       </c>
     </row>
   </sheetData>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sin metadata</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>

--- a/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
+++ b/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,6 +2019,24 @@
         <v>270</v>
       </c>
       <c r="D89" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SRR26147254</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3.851288511500206</v>
+      </c>
+      <c r="C90" t="n">
+        <v>137</v>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -2065,7 +2083,7 @@
         <v>928</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8818941220889477</v>
+        <v>0.7416719182569518</v>
       </c>
     </row>
     <row r="3">
@@ -2075,10 +2093,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4836411750614761</v>
+        <v>0.5903541776319798</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,10 +2142,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.526764884681186</v>
+        <v>0.5222491285991915</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07848293389245389</v>
+        <v>0.0677029363199028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2142,10 +2160,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3571455209533855</v>
+        <v>-0.362601011911577</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0059997761157689</v>
+        <v>0.008249923378517701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2160,10 +2178,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3556316220333446</v>
+        <v>-0.3611350647307009</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01168261989886</v>
+        <v>0.0130959729330461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2178,10 +2196,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3666950874251473</v>
+        <v>-0.37180145310381</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0360504689195915</v>
+        <v>0.0377022110023141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2196,10 +2214,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3389182162553093</v>
+        <v>-0.3446161377363971</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0012785690026345</v>
+        <v>0.0022452234552636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2214,10 +2232,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3334311907284065</v>
+        <v>-0.3391980937899005</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.014844094137967</v>
+        <v>-0.0130304219292357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2232,10 +2250,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.351409065075332</v>
+        <v>-0.3570320783533903</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0145091141961304</v>
+        <v>0.0147252799585398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2250,10 +2268,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3458503772806205</v>
+        <v>-0.351567734651236</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.000792091351191</v>
+        <v>0.000374057530914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2268,10 +2286,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3164227007898983</v>
+        <v>-0.3222217426110267</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0067208052490564</v>
+        <v>-0.0059121573147932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2286,10 +2304,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3712126261586861</v>
+        <v>-0.3765715510260246</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0205664059873644</v>
+        <v>0.0221946299154357</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2304,10 +2322,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4267466762119653</v>
+        <v>0.4188635332301864</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1428154062552804</v>
+        <v>-0.1536276377487452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2322,10 +2340,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3444886565496472</v>
+        <v>-0.350292097015856</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0033762858025169</v>
+        <v>-0.0026046901110309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2340,10 +2358,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4777117795488325</v>
+        <v>0.4712421575258247</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0486424699175851</v>
+        <v>-0.0596209434746878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2358,10 +2376,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4427576725726542</v>
+        <v>0.4369718600451653</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0222657017554233</v>
+        <v>-0.0305641436497033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2376,10 +2394,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4328717887270863</v>
+        <v>0.4253226302976307</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1356854405245421</v>
+        <v>-0.144767467513849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2394,10 +2412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4522583221058521</v>
+        <v>0.4447834520471366</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1124166811498177</v>
+        <v>-0.1234836464900821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,10 +2430,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4415395319018175</v>
+        <v>0.4340145149262327</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1097574462742458</v>
+        <v>-0.1208983785039641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,10 +2448,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4721243125438386</v>
+        <v>0.4654941659400941</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0465683535326869</v>
+        <v>-0.0584055472574914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2448,10 +2466,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4671789981864702</v>
+        <v>0.4608620718762069</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0660703758122592</v>
+        <v>-0.0741248972774517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2466,10 +2484,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3440677259696584</v>
+        <v>-0.3496804111158073</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0078011763344355</v>
+        <v>0.008844450761122599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2484,10 +2502,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3721080573335003</v>
+        <v>-0.3771611672897799</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0295143840084383</v>
+        <v>0.0321390773050391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2502,10 +2520,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3599939648182679</v>
+        <v>-0.3655884371565321</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0069105231543943</v>
+        <v>0.008282349418514001</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2520,10 +2538,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3683226542624468</v>
+        <v>-0.3737383703159102</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0175311401969889</v>
+        <v>0.0189607102071834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2538,10 +2556,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3219369307892852</v>
+        <v>-0.3277873403118663</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0111315062550653</v>
+        <v>-0.0102814292870056</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2556,10 +2574,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3572096959350049</v>
+        <v>-0.3626333914019654</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0209317482057552</v>
+        <v>0.021975241880053</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2574,10 +2592,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3685928685381561</v>
+        <v>-0.3737915545329855</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0148538844917906</v>
+        <v>0.0177445969392085</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2592,10 +2610,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.510907172899751</v>
+        <v>0.5053683175139272</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0269048572763982</v>
+        <v>0.0144072436939468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2610,10 +2628,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.360608917320454</v>
+        <v>-0.3661691073750213</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0061733324488177</v>
+        <v>0.0077673395972987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2628,10 +2646,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5165452539468548</v>
+        <v>0.5108204697924832</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0398429097805983</v>
+        <v>0.0249841699790669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2646,10 +2664,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5279040109553492</v>
+        <v>0.523386280767542</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0924557252033005</v>
+        <v>0.0805893872964427</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2664,10 +2682,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4990304997156333</v>
+        <v>0.4986809515884938</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3738018096702821</v>
+        <v>0.3622638214827788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2682,10 +2700,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5134443784813665</v>
+        <v>0.5128732732568476</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3392194395867624</v>
+        <v>0.3291959043260803</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2700,10 +2718,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3725477710083451</v>
+        <v>-0.3778832900883542</v>
       </c>
       <c r="C34" t="n">
-        <v>0.024363460936333</v>
+        <v>0.0258304547336313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2718,10 +2736,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3446704116049442</v>
+        <v>-0.3500860589106652</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0253123708007231</v>
+        <v>0.025779275147686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2736,10 +2754,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3645738571996244</v>
+        <v>-0.3701000244215163</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0097779739795883</v>
+        <v>0.0112795191464974</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2754,10 +2772,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3519313543445964</v>
+        <v>-0.3574818733598263</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0017708139722194</v>
+        <v>0.0037534208218942</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2772,10 +2790,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3684246077340423</v>
+        <v>-0.3737194249448545</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0091588956727752</v>
+        <v>0.0121013274062649</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2790,10 +2808,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3512947754818393</v>
+        <v>-0.3569356073623038</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0019922049568798</v>
+        <v>0.0033594421262215</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2808,10 +2826,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3793340960097429</v>
+        <v>-0.3843224465656858</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0395560704117379</v>
+        <v>0.0417686950154318</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2826,10 +2844,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5214751954409832</v>
+        <v>0.5171359437388973</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0726001173259738</v>
+        <v>0.0632846124029328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2844,10 +2862,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.3690733252201084</v>
+        <v>-0.3742841547624421</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0264440150339182</v>
+        <v>0.0280946500391129</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2862,10 +2880,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.327571608918711</v>
+        <v>-0.3332534795914811</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0055327746157848</v>
+        <v>-0.0040890558205845</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2880,10 +2898,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3267761718374953</v>
+        <v>-0.3324227462973434</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.008975354721219801</v>
+        <v>-0.0069856467369503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2898,10 +2916,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.515108886870568</v>
+        <v>0.514252721780415</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3457324977229785</v>
+        <v>0.3333588197644956</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2916,10 +2934,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5209584369697392</v>
+        <v>0.5201120179506254</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3341340705637855</v>
+        <v>0.3229312562019852</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2934,10 +2952,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.34808972601082</v>
+        <v>-0.3536978463071975</v>
       </c>
       <c r="C47" t="n">
-        <v>0.007876875096746999</v>
+        <v>0.0087860619476114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2952,10 +2970,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.3399596686661274</v>
+        <v>-0.3456385745260965</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0028592384685927</v>
+        <v>0.0037173471237946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2970,10 +2988,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.3685368792531704</v>
+        <v>-0.3738987750588919</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0167160696419432</v>
+        <v>0.0185262623410974</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2988,10 +3006,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3670679906656123</v>
+        <v>-0.3725149453174557</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0069602167096795</v>
+        <v>0.0092232858351971</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3006,10 +3024,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3533726959402911</v>
+        <v>0.3446561718487362</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2054963769594079</v>
+        <v>-0.2142764921858865</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3024,10 +3042,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3616990651919713</v>
+        <v>0.3537168862677909</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1644188583084118</v>
+        <v>-0.1724901444441312</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3042,10 +3060,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3826020945880666</v>
+        <v>0.3736378430263035</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.200211342830642</v>
+        <v>-0.2116547227876573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3060,10 +3078,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3426406169215666</v>
+        <v>-0.3483905180891823</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0034959573068942</v>
+        <v>-0.0023863473591923</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3078,10 +3096,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2807890193733869</v>
+        <v>0.271481879450516</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2223407752629387</v>
+        <v>-0.2325949776724896</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3096,10 +3114,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3497443264740413</v>
+        <v>0.3405032766651646</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2045475082327115</v>
+        <v>-0.2174345581583366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3114,10 +3132,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3700911587179484</v>
+        <v>0.3612876937834325</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2161601531868656</v>
+        <v>-0.2252102222049999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3132,10 +3150,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3564142082979051</v>
+        <v>0.3478070618037066</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1849198127174698</v>
+        <v>-0.1948096307394722</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3150,10 +3168,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2291071241196891</v>
+        <v>0.2204818255217839</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1852767249133</v>
+        <v>-0.1934429157173313</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3168,10 +3186,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3571441558117491</v>
+        <v>-0.3627539355845173</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0078119257840393</v>
+        <v>0.0089776829298014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3186,10 +3204,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3561104228724526</v>
+        <v>-0.3617832836931384</v>
       </c>
       <c r="C61" t="n">
-        <v>0.008257630489407501</v>
+        <v>0.009085031132397401</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3204,10 +3222,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.358573815604776</v>
+        <v>-0.3639124985321409</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0066603283857315</v>
+        <v>0.0094184327950436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3222,10 +3240,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3416526068191004</v>
+        <v>-0.34742657460419</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0110306223733589</v>
+        <v>-0.009394505569721399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3240,10 +3258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.367670264013503</v>
+        <v>-0.3731782404700678</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0116961422791693</v>
+        <v>0.0131178671818853</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3258,10 +3276,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3611018715393438</v>
+        <v>-0.3666491906518082</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0052233651941391</v>
+        <v>0.0067368378704879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3276,10 +3294,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3488820765455999</v>
+        <v>-0.3544049534236273</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0017047892802104</v>
+        <v>0.0038144436551404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3294,10 +3312,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3443703982099484</v>
+        <v>-0.3502152406151435</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.009477505140015999</v>
+        <v>-0.0083644371048021</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3312,10 +3330,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3736054671312626</v>
+        <v>-0.3789446941039084</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0279351430473871</v>
+        <v>0.029048275656144</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3330,10 +3348,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3569779075505773</v>
+        <v>0.348319411174537</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1938901000879453</v>
+        <v>-0.203281465317012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3348,10 +3366,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3587238182956199</v>
+        <v>0.3507379103442562</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1822393227536042</v>
+        <v>-0.1885519105452543</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3366,10 +3384,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3601314390630981</v>
+        <v>0.3520205795644216</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1577002433638207</v>
+        <v>-0.1670954805512224</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3384,10 +3402,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3487355332281745</v>
+        <v>0.3400505932574423</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.1997745720204262</v>
+        <v>-0.2089479465547808</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3402,10 +3420,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3415941975116753</v>
+        <v>0.3327641392585372</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2063554027272339</v>
+        <v>-0.215943291896458</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3420,10 +3438,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3573830727031482</v>
+        <v>0.3488489106903126</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1903687308601382</v>
+        <v>-0.1994471856906287</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3438,10 +3456,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4302308848009278</v>
+        <v>0.4229341920927008</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.1097043827510588</v>
+        <v>-0.1194552181143431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3456,10 +3474,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.3720755893513617</v>
+        <v>-0.37697626934897</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0642654979230949</v>
+        <v>0.0645661267447965</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3474,10 +3492,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.375820968815208</v>
+        <v>0.3675615902260061</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1799824499823776</v>
+        <v>-0.1884747023928831</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3492,10 +3510,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.3538216865090206</v>
+        <v>-0.3593912367854852</v>
       </c>
       <c r="C78" t="n">
-        <v>0.007961921370267201</v>
+        <v>0.009399034248061201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3510,10 +3528,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5137857081071431</v>
+        <v>0.5096151446656503</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1026077482150584</v>
+        <v>0.09208650434460609</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3528,10 +3546,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5033589370355919</v>
+        <v>0.4983671681053831</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0647794721750963</v>
+        <v>0.0525546413748327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3546,10 +3564,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5255764809134581</v>
+        <v>0.5199180959977334</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0093905253714484</v>
+        <v>-0.0024135365697526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3564,10 +3582,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.3307221081857616</v>
+        <v>-0.3364936204800934</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.008149528048436499</v>
+        <v>-0.0069978337355166</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3582,10 +3600,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.3653797492002525</v>
+        <v>-0.3707305765070451</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0159716050046907</v>
+        <v>0.0179253616722969</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3600,10 +3618,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0687644083511052</v>
+        <v>0.06494242536854609</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2726312085318033</v>
+        <v>0.2495462726313727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3618,10 +3636,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.3795811215273301</v>
+        <v>-0.3849496065131139</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0260672822692985</v>
+        <v>0.0272236265695427</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3636,10 +3654,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4996068617951564</v>
+        <v>0.4985734150238414</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3478417181300083</v>
+        <v>0.3348055602764631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3654,10 +3672,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5135454384737363</v>
+        <v>0.5130464844623488</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3606380791457189</v>
+        <v>0.3497344253197367</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3672,10 +3690,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.511847582020571</v>
+        <v>0.511973216756508</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3560756664051074</v>
+        <v>0.3488358003622397</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3690,12 +3708,30 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.3480006607136804</v>
+        <v>-0.3535661591140139</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0038493985153812</v>
+        <v>0.005569365254011</v>
       </c>
       <c r="D89" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SRR26147254</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.5039131842277874</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.3533793409740647</v>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>CS</t>
         </is>

--- a/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
+++ b/Anexo_10_Diversidad_PRJNA1020132/Anexo_10_Diversidad_PRJNA1020132.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1919,50 +1919,50 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRR26147470</t>
+          <t>SRR26147481</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4.203876500464943</v>
+        <v>4.075283745806841</v>
       </c>
       <c r="C84" t="n">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SRR26147481</t>
+          <t>SRR26147483</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4.075283745806841</v>
+        <v>4.460856250790559</v>
       </c>
       <c r="C85" t="n">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SRR26147483</t>
+          <t>SRR26147494</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.460856250790559</v>
+        <v>4.462086775311617</v>
       </c>
       <c r="C86" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -1973,32 +1973,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRR26147494</t>
+          <t>SRR26147505</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4.462086775311617</v>
+        <v>4.004017774919607</v>
       </c>
       <c r="C87" t="n">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRR26147505</t>
+          <t>SRR26147516</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4.004017774919607</v>
+        <v>4.566283715768781</v>
       </c>
       <c r="C88" t="n">
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2009,34 +2009,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRR26147516</t>
+          <t>SRR26147254</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4.566283715768781</v>
+        <v>3.851288511500206</v>
       </c>
       <c r="C89" t="n">
-        <v>270</v>
+        <v>137</v>
       </c>
       <c r="D89" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SRR26147254</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>3.851288511500206</v>
-      </c>
-      <c r="C90" t="n">
-        <v>137</v>
-      </c>
-      <c r="D90" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
@@ -2110,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2142,10 +2124,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5222491285991915</v>
+        <v>0.5229960139360444</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0677029363199028</v>
+        <v>0.0738649407735649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2160,10 +2142,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.362601011911577</v>
+        <v>-0.3618344757044359</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008249923378517701</v>
+        <v>0.0121152143813919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2178,10 +2160,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3611350647307009</v>
+        <v>-0.3603748013892208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0130959729330461</v>
+        <v>0.0167343890578071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2196,10 +2178,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.37180145310381</v>
+        <v>-0.3711228591596678</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0377022110023141</v>
+        <v>0.0393709774330885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2214,10 +2196,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3446161377363971</v>
+        <v>-0.3438771037115113</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0022452234552636</v>
+        <v>0.005107583449481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2232,10 +2214,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3391980937899005</v>
+        <v>-0.3384188392137288</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0130304219292357</v>
+        <v>-0.0095418037310049</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2250,10 +2232,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3570320783533903</v>
+        <v>-0.3563938196638546</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0147252799585398</v>
+        <v>0.0145296584270223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2268,10 +2250,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.351567734651236</v>
+        <v>-0.3507820265646202</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000374057530914</v>
+        <v>0.0046229564784382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2286,10 +2268,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3222217426110267</v>
+        <v>-0.3214213957945153</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0059121573147932</v>
+        <v>-0.0013693893494122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2304,10 +2286,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3765715510260246</v>
+        <v>-0.375877702397973</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0221946299154357</v>
+        <v>0.0241217204208932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2322,10 +2304,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4188635332301864</v>
+        <v>0.4195203659942819</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1536276377487452</v>
+        <v>-0.1580832060193553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2340,10 +2322,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.350292097015856</v>
+        <v>-0.3495384537403372</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0026046901110309</v>
+        <v>0.0003822715986084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2358,10 +2340,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4712421575258247</v>
+        <v>0.4719629478223058</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0596209434746878</v>
+        <v>-0.0587344518513999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2376,10 +2358,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4369718600451653</v>
+        <v>0.437839167929311</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0305641436497033</v>
+        <v>-0.0237329044107115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2394,10 +2376,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4253226302976307</v>
+        <v>0.4262346030301449</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.144767467513849</v>
+        <v>-0.1406751045211512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,10 +2394,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4447834520471366</v>
+        <v>0.4455647719347447</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1234836464900821</v>
+        <v>-0.1229092169188364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,10 +2412,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4340145149262327</v>
+        <v>0.4349369587448958</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1208983785039641</v>
+        <v>-0.1155977588211844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,10 +2430,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4654941659400941</v>
+        <v>0.4662887459974412</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0584055472574914</v>
+        <v>-0.0549536504732494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,10 +2448,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4608620718762069</v>
+        <v>0.4617926771468919</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0741248972774517</v>
+        <v>-0.066787372625304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2484,10 +2466,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3496804111158073</v>
+        <v>-0.3489107522926493</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008844450761122599</v>
+        <v>0.0129095975110355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2502,10 +2484,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3771611672897799</v>
+        <v>-0.3764681417438922</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0321390773050391</v>
+        <v>0.0342966830182013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,10 +2502,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3655884371565321</v>
+        <v>-0.3648348375461132</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008282349418514001</v>
+        <v>0.0115984392122818</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2538,10 +2520,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3737383703159102</v>
+        <v>-0.3730849620787334</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0189607102071834</v>
+        <v>0.0194964397764567</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2556,10 +2538,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3277873403118663</v>
+        <v>-0.3270377950853173</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0102814292870056</v>
+        <v>-0.0075235927092903</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2574,10 +2556,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3626333914019654</v>
+        <v>-0.3619279013904891</v>
       </c>
       <c r="C26" t="n">
-        <v>0.021975241880053</v>
+        <v>0.0242002850493846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2592,10 +2574,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3737915545329855</v>
+        <v>-0.3731084355837146</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0177445969392085</v>
+        <v>0.0190144805378309</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2610,10 +2592,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5053683175139272</v>
+        <v>0.5060133315588624</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0144072436939468</v>
+        <v>0.0152934757182744</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2628,10 +2610,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3661691073750213</v>
+        <v>-0.3654314848506564</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0077673395972987</v>
+        <v>0.0106043799158328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2646,10 +2628,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5108204697924832</v>
+        <v>0.5114039001821503</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0249841699790669</v>
+        <v>0.024187310665958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2664,10 +2646,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.523386280767542</v>
+        <v>0.5241298441005953</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0805893872964427</v>
+        <v>0.08736248985548339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2682,10 +2664,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4986809515884938</v>
+        <v>0.4990071107067496</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3622638214827788</v>
+        <v>0.3646644693507068</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2700,10 +2682,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5128732732568476</v>
+        <v>0.5132705513607612</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3291959043260803</v>
+        <v>0.332896305237966</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2718,10 +2700,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3778832900883542</v>
+        <v>-0.3771741536039401</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0258304547336313</v>
+        <v>0.0280674657183958</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2736,10 +2718,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3500860589106652</v>
+        <v>-0.3493960117631237</v>
       </c>
       <c r="C35" t="n">
-        <v>0.025779275147686</v>
+        <v>0.0275431943231213</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2754,10 +2736,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3701000244215163</v>
+        <v>-0.3693848814815364</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0112795191464974</v>
+        <v>0.0135227884861596</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2772,10 +2754,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3574818733598263</v>
+        <v>-0.3567160966477634</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0037534208218942</v>
+        <v>0.0074541707806604</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2790,10 +2772,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3737194249448545</v>
+        <v>-0.372979843411864</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0121013274062649</v>
+        <v>0.0149811331208933</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2808,10 +2790,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.3569356073623038</v>
+        <v>-0.3561873544244985</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0033594421262215</v>
+        <v>0.0064211965422586</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2826,10 +2808,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3843224465656858</v>
+        <v>-0.3836546896982893</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0417686950154318</v>
+        <v>0.0433021706243205</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2844,10 +2826,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5171359437388973</v>
+        <v>0.5178435275306119</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0632846124029328</v>
+        <v>0.0679525737467459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2862,10 +2844,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.3742841547624421</v>
+        <v>-0.3737262234393808</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0280946500391129</v>
+        <v>0.0256542935932587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2880,10 +2862,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3332534795914811</v>
+        <v>-0.3325042536461829</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0040890558205845</v>
+        <v>-0.0010803714592183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2898,10 +2880,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.3324227462973434</v>
+        <v>-0.3316104642432765</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.0069856467369503</v>
+        <v>-0.0021938676214808</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2916,10 +2898,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.514252721780415</v>
+        <v>0.514635626234037</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3333588197644956</v>
+        <v>0.3363156376853302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2934,10 +2916,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5201120179506254</v>
+        <v>0.5205417683574225</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3229312562019852</v>
+        <v>0.327340308042167</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2952,10 +2934,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.3536978463071975</v>
+        <v>-0.3529935980395875</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0087860619476114</v>
+        <v>0.0106302640999862</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2970,10 +2952,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.3456385745260965</v>
+        <v>-0.3449072942258148</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0037173471237946</v>
+        <v>0.0061710444090353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2988,10 +2970,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.3738987750588919</v>
+        <v>-0.3732297178261215</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0185262623410974</v>
+        <v>0.0194509144248879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3006,10 +2988,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3725149453174557</v>
+        <v>-0.3717780207996372</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0092232858351971</v>
+        <v>0.0120763801224773</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3024,10 +3006,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3446561718487362</v>
+        <v>0.345621515724182</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2142764921858865</v>
+        <v>-0.2109680133767003</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3042,10 +3024,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3537168862677909</v>
+        <v>0.354664747203937</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1724901444441312</v>
+        <v>-0.1681564536793252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3060,10 +3042,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3736378430263035</v>
+        <v>0.3744688676789997</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2116547227876573</v>
+        <v>-0.2128537358560546</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3078,10 +3060,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3483905180891823</v>
+        <v>-0.3476275717294556</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0023863473591923</v>
+        <v>0.0009489397568028</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3096,10 +3078,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.271481879450516</v>
+        <v>0.2723124694636057</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2325949776724896</v>
+        <v>-0.2348020323719299</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3114,10 +3096,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3405032766651646</v>
+        <v>0.3410705672443321</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2174345581583366</v>
+        <v>-0.2277406265236787</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3132,10 +3114,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3612876937834325</v>
+        <v>0.3621233470307423</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2252102222049999</v>
+        <v>-0.2265264960242304</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3150,10 +3132,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3478070618037066</v>
+        <v>0.3487929590752669</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1948096307394722</v>
+        <v>-0.1901451600822139</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3168,10 +3150,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2204818255217839</v>
+        <v>0.2214679110322288</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1934429157173313</v>
+        <v>-0.1890708534601972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3186,10 +3168,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3627539355845173</v>
+        <v>-0.3620096086255092</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0089776829298014</v>
+        <v>0.0120361608795959</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3204,10 +3186,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3617832836931384</v>
+        <v>-0.3609898457507681</v>
       </c>
       <c r="C61" t="n">
-        <v>0.009085031132397401</v>
+        <v>0.0136251995182946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3222,10 +3204,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3639124985321409</v>
+        <v>-0.363196632908119</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0094184327950436</v>
+        <v>0.0116008883281653</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3240,10 +3222,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.34742657460419</v>
+        <v>-0.3466487470346797</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.009394505569721399</v>
+        <v>-0.0056871017791694</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3258,10 +3240,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3731782404700678</v>
+        <v>-0.3724727825328167</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0131178671818853</v>
+        <v>0.0148722116146762</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3276,10 +3258,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3666491906518082</v>
+        <v>-0.3659922124696019</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0067368378704879</v>
+        <v>0.0066038330230121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3294,10 +3276,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3544049534236273</v>
+        <v>-0.3536059259558459</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0038144436551404</v>
+        <v>0.0084790459241126</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3312,10 +3294,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3502152406151435</v>
+        <v>-0.3494399028212128</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0083644371048021</v>
+        <v>-0.0047929570988823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3330,10 +3312,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3789446941039084</v>
+        <v>-0.3782732024743931</v>
       </c>
       <c r="C68" t="n">
-        <v>0.029048275656144</v>
+        <v>0.0302446392075962</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3348,10 +3330,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.348319411174537</v>
+        <v>0.3493176432181773</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.203281465317012</v>
+        <v>-0.1985775396987608</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3366,10 +3348,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3507379103442562</v>
+        <v>0.3518009099944799</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1885519105452543</v>
+        <v>-0.1807651664102198</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3384,10 +3366,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3520205795644216</v>
+        <v>0.3529187740761537</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1670954805512224</v>
+        <v>-0.1640452036532866</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3402,10 +3384,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3400505932574423</v>
+        <v>0.3409821957903846</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2089479465547808</v>
+        <v>-0.2066911519914248</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3420,10 +3402,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3327641392585372</v>
+        <v>0.3335861132019136</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.215943291896458</v>
+        <v>-0.2174300500201145</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3438,10 +3420,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3488489106903126</v>
+        <v>0.349809496289572</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1994471856906287</v>
+        <v>-0.1956567467618906</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3456,10 +3438,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4229341920927008</v>
+        <v>0.4238211876715079</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.1194552181143431</v>
+        <v>-0.1152523803652523</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3474,10 +3456,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.37697626934897</v>
+        <v>-0.3764209701398883</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0645661267447965</v>
+        <v>0.0630372833353172</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3492,10 +3474,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3675615902260061</v>
+        <v>0.3685264937320304</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1884747023928831</v>
+        <v>-0.1840071760688919</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3510,10 +3492,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.3593912367854852</v>
+        <v>-0.3586077529210646</v>
       </c>
       <c r="C78" t="n">
-        <v>0.009399034248061201</v>
+        <v>0.0139195404261641</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3528,10 +3510,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5096151446656503</v>
+        <v>0.5103764803001766</v>
       </c>
       <c r="C79" t="n">
-        <v>0.09208650434460609</v>
+        <v>0.0997099575602633</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3546,10 +3528,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4983671681053831</v>
+        <v>0.4990381260391591</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0525546413748327</v>
+        <v>0.0556939839622592</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3564,10 +3546,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5199180959977334</v>
+        <v>0.5206716165451901</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.0024135365697526</v>
+        <v>0.0012474728064278</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3582,10 +3564,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.3364936204800934</v>
+        <v>-0.3357274326120671</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0069978337355166</v>
+        <v>-0.0037191310108195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3600,10 +3582,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.3707305765070451</v>
+        <v>-0.3700470783029939</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0179253616722969</v>
+        <v>0.0193534898970653</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3614,50 +3596,50 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRR26147470</t>
+          <t>SRR26147481</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.06494242536854609</v>
+        <v>-0.3842934975058438</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2495462726313727</v>
+        <v>0.0279618777568974</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SRR26147481</t>
+          <t>SRR26147483</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.3849496065131139</v>
+        <v>0.4990354844645381</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0272236265695427</v>
+        <v>0.3408304750000555</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>CSSwP</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SRR26147483</t>
+          <t>SRR26147494</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4985734150238414</v>
+        <v>0.5136042322328507</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3348055602764631</v>
+        <v>0.3595458584215754</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3668,32 +3650,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRR26147494</t>
+          <t>SRR26147505</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5130464844623488</v>
+        <v>0.5124431461071378</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3497344253197367</v>
+        <v>0.3555707328048187</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CSSwP</t>
+          <t>CS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRR26147505</t>
+          <t>SRR26147516</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.511973216756508</v>
+        <v>-0.3527848792850183</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3488358003622397</v>
+        <v>0.009934006781294399</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3704,34 +3686,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRR26147516</t>
+          <t>SRR26147254</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.3535661591140139</v>
+        <v>0.5043902375479073</v>
       </c>
       <c r="C89" t="n">
-        <v>0.005569365254011</v>
+        <v>0.3605974661508406</v>
       </c>
       <c r="D89" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SRR26147254</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0.5039131842277874</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.3533793409740647</v>
-      </c>
-      <c r="D90" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
